--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512416_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512416_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5035</v>
+        <v>1.7967</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3014</v>
+        <v>3.504</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7978</v>
+        <v>-1.7073</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4208</v>
+        <v>2.4189</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3005</v>
+        <v>3.3199</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8797</v>
+        <v>-0.901</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2404</v>
+        <v>5.3283</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3291</v>
+        <v>3.3965</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9112</v>
+        <v>1.9317</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.8195</v>
+        <v>-2.9094</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0286</v>
+        <v>-0.0766</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.7909</v>
+        <v>-2.8327</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.663</v>
+        <v>-2.6319</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.097</v>
+        <v>-4.049</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3231</v>
+        <v>0.5685</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4933</v>
+        <v>0.5327</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8298</v>
+        <v>0.0358</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6647</v>
+        <v>1.6921</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.141</v>
+        <v>1.7701</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1841</v>
+        <v>4.7477</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.0431</v>
+        <v>-2.9776</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3918</v>
+        <v>-1.4034</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2099</v>
+        <v>1.2248</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.6017</v>
+        <v>-2.6282</v>
       </c>
       <c r="J3" t="n">
-        <v>0.493</v>
+        <v>0.5512</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0712</v>
+        <v>1.124</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5782</v>
+        <v>-0.5728</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8847</v>
+        <v>-1.9546</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1388</v>
+        <v>0.1008</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0235</v>
+        <v>-2.0553</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2048</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5621</v>
+        <v>0.0563</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.007</v>
+        <v>0.448</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5551</v>
+        <v>-0.3917</v>
       </c>
       <c r="V3" t="n">
-        <v>3.2998</v>
+        <v>3.3197</v>
       </c>
       <c r="W3" t="n">
-        <v>4.7224</v>
+        <v>4.7608</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4227</v>
+        <v>-1.4411</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2618</v>
+        <v>-0.1758</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0474</v>
+        <v>1.0807</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3091</v>
+        <v>-1.2564</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.2786</v>
+        <v>-2.2704</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8809</v>
+        <v>-0.8891</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3977</v>
+        <v>-1.3813</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4545</v>
+        <v>-0.3774</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6852</v>
+        <v>-0.6539</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2306</v>
+        <v>0.2765</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8241</v>
+        <v>-1.893</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1957</v>
+        <v>-0.2352</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6283</v>
+        <v>-1.6578</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0411</v>
+        <v>0.1069</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7552</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7141</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7709</v>
+        <v>1.7853</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3337</v>
+        <v>-0.3043</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6051</v>
+        <v>0.502</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9388</v>
+        <v>-0.8064</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1316</v>
+        <v>-0.7945</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2847</v>
+        <v>-0.4544</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4163</v>
+        <v>-0.3401</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1528</v>
+        <v>0.6786</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0343</v>
+        <v>-0.5538</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1185</v>
+        <v>1.2324</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2844</v>
+        <v>-1.4731</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2504</v>
+        <v>0.0994</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5348</v>
+        <v>-1.5725</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2048</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8194</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2448</v>
+        <v>-0.1172</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4765</v>
+        <v>-0.1766</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2317</v>
+        <v>0.0593</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>P. UNIACKE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4654</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2718</v>
+        <v>-0.1281</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7372</v>
+        <v>-0.5397</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7816</v>
+        <v>-0.7158</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4488</v>
+        <v>0.0793</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3327</v>
+        <v>-0.7951</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6647999999999999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5602</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.225</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4464</v>
+        <v>-0.7158</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1113</v>
+        <v>0.0793</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5577</v>
+        <v>-0.7951</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6145</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6145</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2984</v>
+        <v>0.048</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.393</v>
+        <v>-0.1281</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0946</v>
+        <v>0.1761</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. UNIACKE</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5692</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.131</v>
+        <v>0.1227</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4382</v>
+        <v>-0.8127</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7068</v>
+        <v>-0.1695</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08359999999999999</v>
+        <v>1.2661</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7903</v>
+        <v>-1.4355</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.1663</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.047</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1193</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7068</v>
+        <v>-1.3358</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.219</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7903</v>
+        <v>-1.5548</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2025</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.8098</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1375</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.131</v>
+        <v>-0.0313</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2685</v>
+        <v>-0.0358</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0639</v>
+        <v>-0.8864</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3607</v>
+        <v>0.7073</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4246</v>
+        <v>-1.5937</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2211</v>
+        <v>-1.2143</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1374</v>
+        <v>1.1461</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3585</v>
+        <v>-2.3604</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8917</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1102</v>
+        <v>1.1635</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2185</v>
+        <v>-0.1843</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1128</v>
+        <v>-2.1936</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0272</v>
+        <v>-0.0175</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1399</v>
+        <v>-2.1761</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0477</v>
+        <v>0.1255</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4933</v>
+        <v>0.7403</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5409</v>
+        <v>-0.6148</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3751</v>
+        <v>-0.9221</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6585</v>
+        <v>1.1424</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0336</v>
+        <v>-2.0645</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1357</v>
+        <v>-0.1168</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1915</v>
+        <v>2.2316</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3272</v>
+        <v>-2.3484</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9439</v>
+        <v>2.0165</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9689</v>
+        <v>2.0328</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.025</v>
+        <v>-0.0163</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0796</v>
+        <v>-2.1333</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2226</v>
+        <v>0.1989</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.3022</v>
+        <v>-2.3322</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6491</v>
+        <v>-0.2102</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8515</v>
+        <v>-0.4569</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2024</v>
+        <v>0.2467</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5903</v>
+        <v>-0.5951</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5903</v>
+        <v>0.5951</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5211</v>
+        <v>-4.9761</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.8391</v>
+        <v>-4.46</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5161</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2284</v>
+        <v>-3.2527</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6379</v>
+        <v>0.614</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.8664</v>
+        <v>-3.8667</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9391</v>
+        <v>-1.9145</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1366</v>
+        <v>0.1383</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0758</v>
+        <v>-2.0528</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2893</v>
+        <v>-1.3382</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5013</v>
+        <v>0.4757</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7906</v>
+        <v>-1.8139</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8194</v>
+        <v>0.8098</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0635</v>
+        <v>-0.5087</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8515</v>
+        <v>-0.521</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2121</v>
+        <v>0.0123</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1565</v>
+        <v>-6.4015</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.517</v>
+        <v>-3.8127</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.6395</v>
+        <v>-2.5888</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3338</v>
+        <v>-4.3441</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1288</v>
+        <v>-1.1268</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.2049</v>
+        <v>-3.2173</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.6822</v>
+        <v>-2.6498</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.4072</v>
+        <v>-1.3848</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.275</v>
+        <v>-1.2649</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6515</v>
+        <v>-1.6943</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2784</v>
+        <v>0.258</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9299</v>
+        <v>-1.9523</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S11" t="n">
-        <v>0.505</v>
+        <v>0.2665</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2137</v>
+        <v>0.8616</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7087</v>
+        <v>-0.5951</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.1022</v>
+        <v>-11.4572</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9419</v>
+        <v>3.405999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-14.0439</v>
+        <v>-14.8632</v>
       </c>
       <c r="G12" t="n">
-        <v>-11.7886</v>
+        <v>-11.8626</v>
       </c>
       <c r="H12" t="n">
-        <v>7.386999999999999</v>
+        <v>7.411500000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-19.1754</v>
+        <v>-19.274</v>
       </c>
       <c r="J12" t="n">
-        <v>5.3108</v>
+        <v>5.778499999999998</v>
       </c>
       <c r="K12" t="n">
-        <v>5.9977</v>
+        <v>6.3096</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6872000000000003</v>
+        <v>-0.5312000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.0991</v>
+        <v>-17.6411</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3893</v>
+        <v>1.1018</v>
       </c>
       <c r="O12" t="n">
-        <v>-18.4881</v>
+        <v>-18.7427</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.1212</v>
+        <v>-5.061299999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.315</v>
+        <v>-13.1595</v>
       </c>
       <c r="R12" t="n">
-        <v>8.193800000000001</v>
+        <v>8.098199999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3692999999999999</v>
+        <v>0.2685</v>
       </c>
       <c r="T12" t="n">
-        <v>1.198</v>
+        <v>1.9537</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.5673</v>
+        <v>-1.6853</v>
       </c>
       <c r="V12" t="n">
-        <v>5.176900000000001</v>
+        <v>5.1982</v>
       </c>
       <c r="W12" t="n">
-        <v>8.7483</v>
+        <v>8.833299999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5716</v>
+        <v>-3.635</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.0708</v>
+        <v>6.9301</v>
       </c>
       <c r="E13" t="n">
-        <v>6.5584</v>
+        <v>6.5556</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5124</v>
+        <v>0.3744</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8894</v>
+        <v>5.9256</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3295</v>
+        <v>-1.3247</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2188</v>
+        <v>7.2502</v>
       </c>
       <c r="J13" t="n">
-        <v>6.5738</v>
+        <v>6.6613</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1583</v>
+        <v>-0.1205</v>
       </c>
       <c r="L13" t="n">
-        <v>6.7321</v>
+        <v>6.7818</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6844</v>
+        <v>-0.7358</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1712</v>
+        <v>-1.2041</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4868</v>
+        <v>0.4684</v>
       </c>
       <c r="P13" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1572</v>
+        <v>-0.0078</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0154</v>
+        <v>-0.1057</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1726</v>
+        <v>0.098</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1715</v>
+        <v>3.7236</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4542</v>
+        <v>3.0083</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7153</v>
       </c>
       <c r="G14" t="n">
-        <v>3.383</v>
+        <v>3.3801</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4691</v>
+        <v>-1.4819</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8521</v>
+        <v>4.862</v>
       </c>
       <c r="J14" t="n">
-        <v>4.0674</v>
+        <v>4.1159</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4373</v>
+        <v>-0.4162</v>
       </c>
       <c r="L14" t="n">
-        <v>4.5047</v>
+        <v>4.5321</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6844</v>
+        <v>-0.7358</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.0318</v>
+        <v>-1.0657</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3474</v>
+        <v>0.33</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5836</v>
+        <v>0.141</v>
       </c>
       <c r="T14" t="n">
-        <v>0.411</v>
+        <v>-0.0954</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1726</v>
+        <v>0.2364</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0627</v>
+        <v>3.396</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7489</v>
+        <v>2.8787</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3138</v>
+        <v>0.5172</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3676</v>
+        <v>3.1626</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1547</v>
+        <v>0.8318</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2128</v>
+        <v>2.3307</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3275</v>
+        <v>3.7044</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0195</v>
+        <v>1.1853</v>
       </c>
       <c r="L15" t="n">
-        <v>1.308</v>
+        <v>2.5191</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0401</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8647</v>
+        <v>-0.3535</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9048</v>
+        <v>-0.1883</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.2533</v>
+        <v>1.4172</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.097</v>
+        <v>-1.0123</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8436</v>
+        <v>2.4294</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3562</v>
+        <v>-0.1255</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1464</v>
+        <v>-0.0643</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2098</v>
+        <v>-0.0612</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3046</v>
+        <v>-1.0583</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6647</v>
+        <v>0.2509</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.3601</v>
+        <v>-1.3092</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9719</v>
+        <v>2.7887</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6211</v>
+        <v>1.4853</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3508</v>
+        <v>1.3034</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1679</v>
+        <v>3.4296</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8636</v>
+        <v>1.2033</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3043</v>
+        <v>2.2263</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6394</v>
+        <v>3.4531</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1709</v>
+        <v>2.1105</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4685</v>
+        <v>1.3427</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4715</v>
+        <v>-0.0235</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3073</v>
+        <v>-0.9071</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1642</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4339</v>
+        <v>-2.227</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.0242</v>
+        <v>-4.049</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4582</v>
+        <v>1.8221</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.5733</v>
+        <v>0.2639</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2361</v>
+        <v>0.3891</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3372</v>
+        <v>-0.1252</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0566</v>
+        <v>1.3221</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2421</v>
+        <v>1.6921</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2987</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8128</v>
+        <v>1.6825</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6384</v>
+        <v>2.1289</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8256</v>
+        <v>-0.4464</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0801</v>
+        <v>2.1174</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7112</v>
+        <v>-1.7005</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7914</v>
+        <v>3.8179</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6858</v>
+        <v>2.7763</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.5713</v>
+        <v>-1.5245</v>
       </c>
       <c r="L17" t="n">
-        <v>4.2571</v>
+        <v>4.3008</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6057</v>
+        <v>-0.6589</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1399</v>
+        <v>-0.1761</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2291</v>
+        <v>1.2147</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2533</v>
+        <v>2.227</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3925</v>
+        <v>0.2547</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9768</v>
+        <v>0.3648</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5843</v>
+        <v>-0.1102</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.889</v>
+        <v>-1.9043</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.889</v>
+        <v>-1.9043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1112</v>
+        <v>-0.0009</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9152</v>
+        <v>-0.7029</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.804</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1858</v>
+        <v>-1.1126</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5046</v>
+        <v>-1.9962</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6905</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3406</v>
+        <v>-1.225</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2812</v>
+        <v>-1.6226</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6218</v>
+        <v>0.3975</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1548</v>
+        <v>0.1125</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2235</v>
+        <v>-0.3736</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0687</v>
+        <v>0.4861</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4339</v>
+        <v>1.2147</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4339</v>
+        <v>2.227</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9707</v>
+        <v>0.016</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5746</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6039</v>
+        <v>-0.0772</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4793</v>
+        <v>-0.119</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4411</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4793</v>
+        <v>-1.5602</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3169</v>
+        <v>-0.2444</v>
       </c>
       <c r="E19" t="n">
-        <v>0.018</v>
+        <v>1.3367</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3349</v>
+        <v>-1.5811</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8958</v>
+        <v>0.1829</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0223</v>
+        <v>-0.5135</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8735000000000001</v>
+        <v>0.6964</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4168</v>
+        <v>0.3852</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2009</v>
+        <v>-0.2581</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6177</v>
+        <v>0.6433</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.479</v>
+        <v>-0.2022</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2232</v>
+        <v>-0.2553</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2558</v>
+        <v>0.0531</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2048</v>
+        <v>1.4172</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2048</v>
+        <v>1.4172</v>
       </c>
       <c r="S19" t="n">
-        <v>0.374</v>
+        <v>0.6549</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4348</v>
+        <v>0.9515</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0608</v>
+        <v>-0.2966</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.4994</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.4994</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5074</v>
+        <v>-0.511</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2044</v>
+        <v>-0.2714</v>
       </c>
       <c r="F20" t="n">
-        <v>0.697</v>
+        <v>-0.2395</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0854</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9902</v>
+        <v>-0.0199</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9048</v>
+        <v>-0.8717</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.26</v>
+        <v>-0.3959</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6552</v>
+        <v>0.2166</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3952</v>
+        <v>-0.6126</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1746</v>
+        <v>-0.4957</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3351</v>
+        <v>-0.2365</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5097</v>
+        <v>-0.2591</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2291</v>
+        <v>0.2025</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2533</v>
+        <v>0.2025</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.533</v>
+        <v>0.1782</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3429</v>
+        <v>0.1245</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1902</v>
+        <v>0.0537</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1181</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4227</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-1.1765</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2414</v>
+        <v>-0.4373</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4033</v>
+        <v>-0.7391</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9393</v>
+        <v>-1.9594</v>
       </c>
       <c r="H21" t="n">
+        <v>-1.5015</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.4579</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.4736</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.6723</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1988</v>
+      </c>
+      <c r="M21" t="n">
         <v>-1.4859</v>
       </c>
-      <c r="I21" t="n">
-        <v>-0.4534</v>
-      </c>
-      <c r="J21" t="n">
-        <v>-0.4797</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-0.6772</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.1976</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-1.4596</v>
-      </c>
       <c r="N21" t="n">
-        <v>-0.8087</v>
+        <v>-0.8292</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.651</v>
+        <v>-0.6567</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8849</v>
+        <v>0.3781</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2383</v>
+        <v>0.0362</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6466</v>
+        <v>0.3418</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6296</v>
+        <v>-3.1064</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4644</v>
+        <v>-1.1185</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1652</v>
+        <v>-1.9879</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3647</v>
+        <v>-2.3722</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8922</v>
+        <v>-0.9085</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4725</v>
+        <v>-1.4637</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.379</v>
+        <v>-1.3607</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.379</v>
+        <v>-1.3607</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9857</v>
+        <v>-1.0115</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8922</v>
+        <v>-0.9085</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0935</v>
+        <v>-0.103</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5312</v>
+        <v>0.0026</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3275</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2037</v>
+        <v>0.0113</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9385</v>
+        <v>-0.9393</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1806</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.1023</v>
+        <v>13.4817</v>
       </c>
       <c r="E23" t="n">
-        <v>14.044</v>
+        <v>14.8634</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9418</v>
+        <v>-1.3816</v>
       </c>
       <c r="G23" t="n">
-        <v>11.7886</v>
+        <v>11.8624</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.386700000000001</v>
+        <v>-7.4116</v>
       </c>
       <c r="I23" t="n">
-        <v>19.1753</v>
+        <v>19.2738</v>
       </c>
       <c r="J23" t="n">
-        <v>17.099</v>
+        <v>17.641</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3892</v>
+        <v>-1.1018</v>
       </c>
       <c r="L23" t="n">
-        <v>18.4883</v>
+        <v>18.7428</v>
       </c>
       <c r="M23" t="n">
-        <v>-5.3104</v>
+        <v>-5.7786</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.9976</v>
+        <v>-6.309600000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6871000000000002</v>
+        <v>0.5312</v>
       </c>
       <c r="P23" t="n">
-        <v>5.121</v>
+        <v>5.061499999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>-8.1938</v>
+        <v>-8.0982</v>
       </c>
       <c r="R23" t="n">
-        <v>13.3149</v>
+        <v>13.1596</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3692000000000001</v>
+        <v>1.7561</v>
       </c>
       <c r="T23" t="n">
-        <v>1.5672</v>
+        <v>1.6852</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1981</v>
+        <v>0.0708</v>
       </c>
       <c r="V23" t="n">
-        <v>-5.1769</v>
+        <v>-5.198200000000001</v>
       </c>
       <c r="W23" t="n">
-        <v>3.571600000000001</v>
+        <v>3.635</v>
       </c>
       <c r="X23" t="n">
-        <v>-8.7484</v>
+        <v>-8.833300000000001</v>
       </c>
     </row>
   </sheetData>
